--- a/public/techmap/techmap_request_template.xlsx
+++ b/public/techmap/techmap_request_template.xlsx
@@ -66,17 +66,15 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,8 +459,9 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -543,16 +542,21 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Requester</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t># 설명행(삭제 가능)</t>
@@ -560,7 +564,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ADD / CHANGE_DISPLAY / RETIRE</t>
+          <t>ADD / CHANGE_DISPLAY / RETIRE / HIDE / SHOW / OPTION_ADD / OPTION_REMOVE</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -575,42 +579,42 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ADD · 신규 Layer일 때 techLayers 번호</t>
+          <t>Master ADD · 신규 Layer 번호 (DK는 비우면 Master에서)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>ADD · 신규 Layer 약어 (비우면 Layer 이름)</t>
+          <t>Master ADD · 신규 Layer 약어</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>ADD · 신규 Purpose일 때 techPurposes 번호</t>
+          <t>Master ADD · 신규 Purpose 번호</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>ADD · layermap stream 번호</t>
+          <t>Master ADD · stream 번호 (DK는 비우면 Master에서)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>ADD · layermap datatype</t>
+          <t>Master ADD · datatype</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>기존 packet 재사용 시 이름 / CHANGE에서 공유 packet 직접 수정 시 현재 이름</t>
+          <t>기존 packet 재사용 / 공유 packet 직접 수정 시 현재 이름</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>색 이름 또는 #RRGGBB 또는 R,G,B</t>
+          <t>색 이름 · #RRGGBB · R,G,B (DK ADD에서 비우면 Master 표시)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>비우면 Fill_Color와 동일</t>
+          <t>비우면 Fill_Color와 같게</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -625,15 +629,20 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>선택 · outline / solid / X / stipple / outlineStipple ...</t>
+          <t>outline / solid / X / stipple / outlineStipple …</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>요청자</t>
+          <t>OPTION_ADD/REMOVE 대상 Option 이름</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>요청자 / Site</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>요청 사유 / Site Request 원문 요약</t>
         </is>
@@ -642,7 +651,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ADD,CHANGE_DISPLAY,RETIRE"</formula1>
+      <formula1>"ADD,CHANGE_DISPLAY,RETIRE,HIDE,SHOW,OPTION_ADD,OPTION_REMOVE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -655,12 +664,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +680,12 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>필수 컬럼</t>
+          <t>쓰는 곳</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>처리 내용</t>
+          <t>처리</t>
         </is>
       </c>
     </row>
@@ -688,12 +697,12 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Layer, Purpose (+신규 Layer면 Layer_No) , GDS_Layer/Datatype, Fill_Color 또는 Packet</t>
+          <t>Master · DK</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>techLayers·techPurposes(필요 시)·techLayerPurposePriorities·techDisplays·layermap·drDefinePacket/Color 추가</t>
+          <t>Master: 번호를 직접 정함(Layer_No·GDS 필수). DK: Layer·Purpose만 쓰면 번호·GDS·표시를 Master에서 가져옴, 다르게 쓰면 ERROR</t>
         </is>
       </c>
     </row>
@@ -705,12 +714,12 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Layer, Purpose + 바꿀 항목(Fill/Outline/Stipple/LineStyle/Fill_Style)</t>
+          <t>Master · DK</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>packet을 다른 LPP와 공유하면 전용 packet을 새로 만들어 연결(검토 필요). Packet 칸에 현재 packet 이름을 적으면 공유 packet을 직접 수정</t>
+          <t>packet 색·패턴 변경. 공유 packet이면 전용 packet 생성(검토 필요)</t>
         </is>
       </c>
     </row>
@@ -722,12 +731,46 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Layer (+Purpose, 비우면 Layer 전체)</t>
+          <t>Master · DK</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>techfile 해당 행을 삭제하지 않고 주석 처리. layermap은 기본 유지(설정에서 변경). 다른 곳에서 참조되면 검토 필요</t>
+          <t>지우지 않고 주석 처리 + RETIRED 표시. Purpose를 비우면 Layer 전체</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>HIDE / SHOW</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Master · DK</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>techDisplays Vis·Sel 플래그 nil / t (Layer는 남고 사용자 화면에서 숨김·선택 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>OPTION_ADD / OPTION_REMOVE</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Option(Metal/Via Stack) 정의에 Layer 예외 넣기/빼기 — Option 칸 필수</t>
         </is>
       </c>
     </row>
